--- a/Enhanced_Listings.xlsx
+++ b/Enhanced_Listings.xlsx
@@ -425,13 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Ships_From</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -441,37 +446,34 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ships_From</t>
+          <t>Product_Title</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Product_Title</t>
+          <t>Seller_Name</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Seller_Name</t>
+          <t>Image_1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Image_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>Image_2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/2L-High-Speed-Blender-Heavy-Duty-Ice-Crushing-Juicer-Smoothie-Maker-Food-Processor-Multifunction-Pengisar-Mixer-i.1714340390.54208947162?extraParams=%7B%22display_model_id%22%3A405792851667%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://shopee.sg/2L-High-Speed-Blender-Heavy-Duty-Ice-Crushing-Juicer-Smoothie-Maker-Food-Processor-Multifunction-Pengisar-Mixer-i.1714340390.54208947162?extraParams=%7B%22display_model_id%22%3A405792851667%2C%22model_selection_logic%22%3A3%7D</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,39 +483,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2L High Speed Blender Heavy Duty Ice Crushing Juicer Smoothie Maker Food Processor Multifunction Pengisar Mixer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SY98.SG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>images\0-0.png</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>images\0-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/Fully-Automatic-Soy-Milk-Maker-Portable-Juicer-Blender-Machine-Smart-Soya-Bean-Milk-Machine-i.299068664.50058759450?extraParams=%7B%22display_model_id%22%3A420778894384%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2L High Speed Blender Heavy Duty Ice Crushing Juicer Smoothie Maker Food Processor Multifunction Pengisar Mixer</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SY98.SG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>images\0-0.png</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>images\0-1.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://shopee.sg/Fully-Automatic-Soy-Milk-Maker-Portable-Juicer-Blender-Machine-Smart-Soya-Bean-Milk-Machine-i.299068664.50058759450?extraParams=%7B%22display_model_id%22%3A420778894384%2C%22model_selection_logic%22%3A3%7D</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>112233</t>
@@ -521,27 +520,224 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Fully Automatic Soy Milk Maker Portable Juicer Blender Machine Smart Soya Bean Milk Machine</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SG Home Selling</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>images\1-0.png</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>images\1-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/%E8%B1%86%E6%B5%86%E6%9C%BA%E5%AE%B6%E7%94%A8%E5%85%A8%E8%87%AA%E5%8A%A8%E5%85%8D%E7%85%AE%E5%85%8D%E6%BB%A4%E9%9D%99%E9%9F%B3%E6%97%A0%E6%B8%A3%E8%BF%B7%E4%BD%A0%E5%A4%9A%E5%8A%9F%E8%83%BD%E6%A6%A8%E6%B1%81%E5%B0%8F%E5%9E%8B%E7%A0%B4%E5%A3%81%E6%9C%BA-i.1257795465.46357553994?extraParams=%7B%22display_model_id%22%3A370671036105%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mainland China</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>豆浆机家用全自动免煮免飞静音无渣迷你多功能榨汁小型破壁机i</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>csdiohjkbf.sg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>images\2-0.png</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>images\2-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/%E7%A0%B4%E5%A3%81%E6%9C%BA%E6%A6%A8%E6%B1%81%E6%9C%BA%E4%B8%80%E4%BD%93%E5%AE%B6%E7%94%A8%E9%9D%99%E9%9F%B32025%E5%85%A8%E8%87%AA%E5%8A%A8%E5%B0%8F%E5%9E%8B%E6%97%A0%E6%B8%A3%E5%85%8D%E7%85%AE%E8%B1%86%E6%B5%86%E6%9C%BA-i.1257795465.49057544515?extraParams=%7B%22display_model_id%22%3A345671036006%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mainland China</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>破壁机榨汁机一体家用静音2025全自动小型无渣免煮豆浆机</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>csdiohjkbf.sg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>images\3-0.png</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>images\3-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/%E5%A4%A7%E5%AE%87%E7%A0%B4%E5%A3%81%E6%9C%BA%E5%AE%B6%E7%94%A8%E5%B0%8F%E5%9E%8B%E8%B1%86%E6%B5%86%E6%9C%BA%E5%85%A8%E8%87%AA%E5%8A%A8%E8%BF%B7%E4%BD%A0%E9%9D%9E%E9%9D%99%E4%BD%8E%E5%99%AA%E9%9F%B3%E6%97%A0%E6%B8%A3%E6%96%B0%E6%AC%BE%E6%A6%A8%E6%B1%81%E7%B1%B3%E7%B3%8ADaewoo-wall-breaking-machine-household-small-soybean-milk-machine-automatic20251127-i.1257795465.53052198783?extraParams=%7B%22display_model_id%22%3A445213452026%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mainland China</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>大宇破壁机家用小型豆浆机全自动迷你非静音无噪音无渣新款榨汁米糊Daewoo wall-breaking machine household small soybean milk machine...</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>csdiohjbkbf.sg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>images\4-0.png</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>images\4-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/%E3%80%90BRUNO%E3%80%91Soy-Milk-Maker-Machine-1000ml-High-Speed-Blender-Multifunctional-Food-Processor-High-borosilicate-Glass-Liner-i.1343862364.54707001967?extraParams=%7B%22display_model_id%22%3A208812747787%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[BRUNO] Soy Milk Maker Machine 1000ml High Speed Blender Multifunctional Food Processor High borosilicate Glass Liner</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>POPOLO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>images\5-0.png</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>images\5-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/%E3%80%90BRUNO%E3%80%91Soy-Milk-Maker-Machine-Blender-Milk-Pot-Jug-Soya-Bean-Machine-600-1000ml-316-Stainless-Steel-i.1343862364.44129362157?extraParams=%7B%22display_model_id%22%3A345658530595%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[BRUNO] Soy Milk Maker Machine Blender Milk Pot Jug Soya Bean Machine 600/1000ml 316 Stainless Steel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>POPOLO.HOME.SG</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>images\6-0.png</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>images\6-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://shopee.sg/NEW-Mini-soymilk-maker-1600ml-blender-heating-blender-Multifunctional-wall-breaker-48-blades-i.1457582756.56909241870?extraParams=%7B%22display_model_id%22%3A350817897757%2C%22model_selection_logic%22%3A3%7D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fully Automatic Soy Milk Maker Portable Juicer Blender Machine Smart Soya Bean Milk Machine</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SG Home Selling</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>images\1-0.png</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>images\1-1.png</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>688686</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NEW Mini soymilk maker 1600ml blender heating blender Multifunctional wall breaker 48 blades</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7IVER.SG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>images\7-0.png</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>images\7-1.png</t>
         </is>
       </c>
     </row>

--- a/Enhanced_Listings.xlsx
+++ b/Enhanced_Listings.xlsx
@@ -553,7 +553,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>豆浆机家用全自动免煮免飞静音无渣迷你多功能榨汁小型破壁机i</t>
+          <t>豆浆机家用全自动免煮鸡免飞静音无渣迷你多功能榨汁小型破壁机</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,7 +586,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>破壁机榨汁机一体家用静音2025全自动小型无渣免煮豆浆机</t>
+          <t>破壁机榨汁机一体家用静音2025全自动小型无污染免煮豆浆机</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -619,12 +619,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>大宇破壁机家用小型豆浆机全自动迷你非静音无噪音无渣新款榨汁米糊Daewoo wall-breaking machine household small soybean milk machine...</t>
+          <t>大宇破壁机家用小型豆浆机全自动迷你非静音低噪音无渣新款榨汁机米糊Daewoo wall-breaking machine household small soybean milk machine...</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>csdiohjbkbf.sg</t>
+          <t>csdiohjkbf.sg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>POPOLO</t>
+          <t>POPOLO.HOME.SG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
